--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/07/2026</t>
+          <t>Dossier généré le 13/07/2026</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Annonce" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$56</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Synthèse'!$A$1:$C$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0&quot; €/mois&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,12 +38,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001D5240"/>
-      <sz val="16"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="17"/>
     </font>
     <font>
       <b val="1"/>
-      <sz val="12"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -73,12 +73,19 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="13"/>
+      <color rgb="001D5240"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
     <font>
       <i val="1"/>
-      <sz val="11"/>
+      <sz val="10.5"/>
     </font>
     <font>
       <b val="1"/>
@@ -88,7 +95,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +105,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001D5240"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6A532"/>
       </patternFill>
     </fill>
     <fill>
@@ -123,43 +135,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment indent="1"/>
+      <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -280,18 +299,21 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1D5240"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Synthèse'!$E$6:$E$8</f>
+              <f>'Synthèse'!$E$7:$E$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Synthèse'!$F$6:$F$8</f>
+              <f>'Synthèse'!$F$7:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -354,7 +376,10 @@
           <idx val="0"/>
           <order val="0"/>
           <spPr>
-            <a:ln>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="1D5240"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -431,7 +456,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="2880000"/>
@@ -766,9 +791,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -776,533 +801,616 @@
     <col width="46" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Dossier de financement — Murs commerciaux</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Local commercial à vendre près métro Gabriel Péri Asnières</t>
-        </is>
-      </c>
+          <t>Les Murs.   Dossier de financement — murs commerciaux</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="3" customHeight="1">
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Asnières-sur-Seine (92600) — annonce geolocaux du 2026-07-06</t>
+          <t>Local commercial à vendre près métro Gabriel Péri Asnières</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Voir l'annonce en ligne</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Dossier généré le 13/07/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+          <t>Asnières-sur-Seine (92600) — annonce geolocaux du 2026-07-06</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Voir l'annonce en ligne ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Dossier généré le 13/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>L'ESSENTIEL — ce que votre conseiller lit en premier</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Loyer mensuel</t>
+        </is>
+      </c>
+      <c r="F7" s="8">
+        <f>IFERROR(B20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Prix d'achat retenu</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <f>B25</f>
+        <v/>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Crédit + charges / mois</t>
+        </is>
+      </c>
+      <c r="F8" s="8">
+        <f>B38-(B43+B44+B45)/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Apport nécessaire</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>B36</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Cash-flow</t>
+        </is>
+      </c>
+      <c r="F9" s="8">
+        <f>B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Mensualité de crédit estimée</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>B38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Cash-flow mensuel attendu</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>B49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>DSCR (≥ 1,20 rassure)</t>
+        </is>
+      </c>
+      <c r="B12" s="12">
+        <f>B54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +142 €/mois.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>LE BIEN</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Loyer mensuel</t>
-        </is>
-      </c>
-      <c r="F6" s="7">
-        <f>IFERROR(B11,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>État locatif</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>Murs libres — local à louer après l'achat</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Crédit + charges / mois</t>
-        </is>
-      </c>
-      <c r="F7" s="7">
-        <f>B28-(B33+B34+B35)/12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B17" s="16" t="n">
         <v>104</v>
       </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Cash-flow</t>
-        </is>
-      </c>
-      <c r="F8" s="7">
-        <f>B39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Prix affiché</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B18" s="17" t="n">
         <v>270000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>Prix au m²</t>
         </is>
       </c>
-      <c r="B10" s="11">
-        <f>IFERROR(B9/B8,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="B19" s="17">
+        <f>IFERROR(B18/B17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Loyer mensuel HT</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B20" s="18" t="n">
         <v>1906.67</v>
       </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>ESTIMATION au loyer de marché local — aucun bail ne le garantit</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Marché local (prix/m²)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>2 198 à 5 747 €/m²</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>ce bien est 39 % SOUS la médiane locale</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Source de la fourchette</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>153 ventes réelles 2023-2025 (DVF)</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>DVF = prix réellement payés, enregistrés chez le notaire (data.gouv.fr)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>HYPOTHÈSES — cellules jaunes à ajuster avec votre conseiller</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>Prix négocié retenu</t>
         </is>
       </c>
-      <c r="B15" s="12" t="n">
+      <c r="B25" s="18" t="n">
         <v>270000</v>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>par défaut le prix affiché — un prix demandé se négocie</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>Frais d'acquisition (notaire, garanties)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
+      <c r="B26" s="20" t="n">
         <v>0.08</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Apport personnel</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
+      <c r="B27" s="20" t="n">
         <v>0.2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Taux du crédit (hors assurance)</t>
         </is>
       </c>
-      <c r="B18" s="14" t="n">
+      <c r="B28" s="20" t="n">
         <v>0.0458</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
         <is>
           <t>Durée du crédit (années)</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B29" s="21" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>Taxe foncière (en mois de loyer par an)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
+      <c r="B30" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>à remplacer par le montant réel dès que connu</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>Provision entretien &amp; vacance (% du loyer)</t>
         </is>
       </c>
-      <c r="B21" s="14" t="n">
+      <c r="B31" s="20" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
         <is>
           <t>Assurance propriétaire (PNO, €/an)</t>
         </is>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B32" s="18" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>PLAN DE FINANCEMENT</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>Coût d'acquisition total</t>
         </is>
       </c>
-      <c r="B25" s="11">
-        <f>B15*(1+B16)</f>
-        <v/>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
+      <c r="B35" s="17">
+        <f>B25*(1+B26)</f>
+        <v/>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>prix négocié + frais d'acquisition</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Apport personnel</t>
         </is>
       </c>
-      <c r="B26" s="11">
-        <f>B25*B17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="B36" s="17">
+        <f>B35*B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="14" t="inlineStr">
         <is>
           <t>Montant emprunté</t>
         </is>
       </c>
-      <c r="B27" s="11">
-        <f>B25-B26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="B37" s="17">
+        <f>B35-B36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Mensualité du crédit</t>
         </is>
       </c>
-      <c r="B28" s="17">
-        <f>IFERROR(-PMT(B18/12,B19*12,B27),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="B38" s="23">
+        <f>IFERROR(-PMT(B28/12,B29*12,B37),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>Service de la dette (annuel)</t>
         </is>
       </c>
-      <c r="B29" s="11">
-        <f>B28*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="B39" s="17">
+        <f>B38*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>EXPLOITATION ANNUELLE</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
         <is>
           <t>Loyers annuels HT</t>
         </is>
       </c>
-      <c r="B32" s="11">
-        <f>IFERROR(B11*12,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="B42" s="17">
+        <f>IFERROR(B20*12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>− Taxe foncière</t>
         </is>
       </c>
-      <c r="B33" s="11">
-        <f>-IFERROR(B11*B20,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="B43" s="17">
+        <f>-IFERROR(B20*B30,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="14" t="inlineStr">
         <is>
           <t>− Entretien &amp; vacance locative</t>
         </is>
       </c>
-      <c r="B34" s="11">
-        <f>-B32*B21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="B44" s="17">
+        <f>-B42*B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="14" t="inlineStr">
         <is>
           <t>− Assurance PNO</t>
         </is>
       </c>
-      <c r="B35" s="11">
-        <f>-B22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="B45" s="17">
+        <f>-B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
         <is>
           <t>Revenu net avant crédit</t>
         </is>
       </c>
-      <c r="B36" s="11">
-        <f>B32+B33+B34+B35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="B46" s="17">
+        <f>B42+B43+B44+B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>− Remboursement du crédit</t>
         </is>
       </c>
-      <c r="B37" s="11">
-        <f>-B29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="B47" s="17">
+        <f>-B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>Cash-flow annuel</t>
         </is>
       </c>
-      <c r="B38" s="11">
-        <f>B36-B29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+      <c r="B48" s="17">
+        <f>B46-B39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="14" t="inlineStr">
         <is>
           <t>Cash-flow mensuel</t>
         </is>
       </c>
-      <c r="B39" s="18">
-        <f>B38/12</f>
-        <v/>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="B49" s="24">
+        <f>B48/12</f>
+        <v/>
+      </c>
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>positif : le bien se paie tout seul, loyer ≥ crédit + charges</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>LES RATIOS QUE REGARDE LE BANQUIER</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>Rendement brut</t>
         </is>
       </c>
-      <c r="B42" s="19">
-        <f>IFERROR(B32/B15,"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
+      <c r="B52" s="25">
+        <f>IFERROR(B42/B25,"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>loyer annuel ÷ prix — la base de comparaison des biens</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Rendement net avant crédit</t>
         </is>
       </c>
-      <c r="B43" s="19">
-        <f>IFERROR(B36/B25,"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="13" t="inlineStr">
+      <c r="B53" s="25">
+        <f>IFERROR(B46/B35,"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>après taxe foncière, entretien et assurance</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>DSCR — couverture de la dette</t>
         </is>
       </c>
-      <c r="B44" s="20">
-        <f>IFERROR(B36/B29,"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="13" t="inlineStr">
+      <c r="B54" s="26">
+        <f>IFERROR(B46/B39,"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>revenu net ÷ crédit : ≥ 1,20 rassure une banque</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
         <is>
           <t>LTV — part financée par la banque</t>
         </is>
       </c>
-      <c r="B45" s="19">
-        <f>IFERROR(B27/B15,"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="13" t="inlineStr">
+      <c r="B55" s="25">
+        <f>IFERROR(B37/B25,"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>≤ 80 % est la zone de confort bancaire</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="14" t="inlineStr">
         <is>
           <t>Effort d'épargne mensuel si négatif</t>
         </is>
       </c>
-      <c r="B46" s="17">
-        <f>MAX(0,-B38/12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="inlineStr">
+      <c r="B56" s="23">
+        <f>MAX(0,-B48/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="14" t="inlineStr">
         <is>
           <t>Score de l'outil de veille</t>
         </is>
       </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>66/100</t>
-        </is>
-      </c>
-      <c r="C47" s="13" t="inlineStr">
-        <is>
-          <t>rendement, emplacement, prix vs marché, proximité</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="21" t="inlineStr">
-        <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +142 €/mois.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50"/>
-    <row r="51"/>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>65/100</t>
+        </is>
+      </c>
+      <c r="C57" s="19" t="inlineStr">
+        <is>
+          <t>rendement, emplacement, prix vs marché, financement, fiscalité</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
+    <mergeCell ref="A4:B4"/>
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A49:C51"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A13:C14"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A51:C51"/>
   </mergeCells>
-  <conditionalFormatting sqref="B38:B39">
+  <conditionalFormatting sqref="B48">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -1310,18 +1418,43 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B44">
+  <conditionalFormatting sqref="B49">
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B54">
+    <cfRule type="cellIs" priority="5" operator="greaterThanOrEqual" dxfId="0">
       <formula>1.2</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B11">
+    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Les Murs. — dossier indicatif généré automatiquement ; l'offre de prêt de la banque fait foi</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
@@ -1344,33 +1477,33 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="27" t="inlineStr">
         <is>
           <t>Année</t>
         </is>
       </c>
-      <c r="B1" s="22" t="inlineStr">
+      <c r="B1" s="27" t="inlineStr">
         <is>
           <t>Capital dû en début d'année</t>
         </is>
       </c>
-      <c r="C1" s="22" t="inlineStr">
+      <c r="C1" s="27" t="inlineStr">
         <is>
           <t>Intérêts de l'année</t>
         </is>
       </c>
-      <c r="D1" s="22" t="inlineStr">
+      <c r="D1" s="27" t="inlineStr">
         <is>
           <t>Capital remboursé</t>
         </is>
       </c>
-      <c r="E1" s="22" t="inlineStr">
+      <c r="E1" s="27" t="inlineStr">
         <is>
           <t>Capital restant dû</t>
         </is>
       </c>
       <c r="G1">
-        <f>'Synthèse'!B19</f>
+        <f>'Synthèse'!B29</f>
         <v/>
       </c>
     </row>
@@ -1378,29 +1511,29 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
-        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$27,"")</f>
-        <v/>
-      </c>
-      <c r="C2" s="7">
+      <c r="B2" s="8">
+        <f>IF(A2&lt;=$G$1,'Synthèse'!$B$37,"")</f>
+        <v/>
+      </c>
+      <c r="C2" s="8">
         <f>IF(A2&lt;=$G$1,B2*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="8">
         <f>IF(A2&lt;=$G$1,MIN(B2,$G$3-C2),"")</f>
         <v/>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="8">
         <f>IF(A2&lt;=$G$1,MAX(0,B2-D2),"")</f>
         <v/>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Tableau indicatif (pas annuel) — l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
       <c r="G2">
-        <f>'Synthèse'!B18</f>
+        <f>'Synthèse'!B28</f>
         <v/>
       </c>
     </row>
@@ -1408,24 +1541,24 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="8">
         <f>IF(A3&lt;=$G$1,E2,"")</f>
         <v/>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="8">
         <f>IF(A3&lt;=$G$1,B3*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="8">
         <f>IF(A3&lt;=$G$1,MIN(B3,$G$3-C3),"")</f>
         <v/>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="8">
         <f>IF(A3&lt;=$G$1,MAX(0,B3-D3),"")</f>
         <v/>
       </c>
       <c r="G3">
-        <f>'Synthèse'!B29</f>
+        <f>'Synthèse'!B39</f>
         <v/>
       </c>
     </row>
@@ -1433,19 +1566,19 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="8">
         <f>IF(A4&lt;=$G$1,E3,"")</f>
         <v/>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="8">
         <f>IF(A4&lt;=$G$1,B4*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="8">
         <f>IF(A4&lt;=$G$1,MIN(B4,$G$3-C4),"")</f>
         <v/>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="8">
         <f>IF(A4&lt;=$G$1,MAX(0,B4-D4),"")</f>
         <v/>
       </c>
@@ -1454,19 +1587,19 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="8">
         <f>IF(A5&lt;=$G$1,E4,"")</f>
         <v/>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="8">
         <f>IF(A5&lt;=$G$1,B5*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="8">
         <f>IF(A5&lt;=$G$1,MIN(B5,$G$3-C5),"")</f>
         <v/>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="8">
         <f>IF(A5&lt;=$G$1,MAX(0,B5-D5),"")</f>
         <v/>
       </c>
@@ -1475,19 +1608,19 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="8">
         <f>IF(A6&lt;=$G$1,E5,"")</f>
         <v/>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="8">
         <f>IF(A6&lt;=$G$1,B6*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>IF(A6&lt;=$G$1,MIN(B6,$G$3-C6),"")</f>
         <v/>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="8">
         <f>IF(A6&lt;=$G$1,MAX(0,B6-D6),"")</f>
         <v/>
       </c>
@@ -1496,19 +1629,19 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <f>IF(A7&lt;=$G$1,E6,"")</f>
         <v/>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>IF(A7&lt;=$G$1,B7*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>IF(A7&lt;=$G$1,MIN(B7,$G$3-C7),"")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="8">
         <f>IF(A7&lt;=$G$1,MAX(0,B7-D7),"")</f>
         <v/>
       </c>
@@ -1517,19 +1650,19 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="8">
         <f>IF(A8&lt;=$G$1,E7,"")</f>
         <v/>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <f>IF(A8&lt;=$G$1,B8*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="8">
         <f>IF(A8&lt;=$G$1,MIN(B8,$G$3-C8),"")</f>
         <v/>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="8">
         <f>IF(A8&lt;=$G$1,MAX(0,B8-D8),"")</f>
         <v/>
       </c>
@@ -1538,19 +1671,19 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="8">
         <f>IF(A9&lt;=$G$1,E8,"")</f>
         <v/>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="8">
         <f>IF(A9&lt;=$G$1,B9*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>IF(A9&lt;=$G$1,MIN(B9,$G$3-C9),"")</f>
         <v/>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="8">
         <f>IF(A9&lt;=$G$1,MAX(0,B9-D9),"")</f>
         <v/>
       </c>
@@ -1559,19 +1692,19 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="8">
         <f>IF(A10&lt;=$G$1,E9,"")</f>
         <v/>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="8">
         <f>IF(A10&lt;=$G$1,B10*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="8">
         <f>IF(A10&lt;=$G$1,MIN(B10,$G$3-C10),"")</f>
         <v/>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="8">
         <f>IF(A10&lt;=$G$1,MAX(0,B10-D10),"")</f>
         <v/>
       </c>
@@ -1580,19 +1713,19 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="8">
         <f>IF(A11&lt;=$G$1,E10,"")</f>
         <v/>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="8">
         <f>IF(A11&lt;=$G$1,B11*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="8">
         <f>IF(A11&lt;=$G$1,MIN(B11,$G$3-C11),"")</f>
         <v/>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="8">
         <f>IF(A11&lt;=$G$1,MAX(0,B11-D11),"")</f>
         <v/>
       </c>
@@ -1601,19 +1734,19 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="8">
         <f>IF(A12&lt;=$G$1,E11,"")</f>
         <v/>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="8">
         <f>IF(A12&lt;=$G$1,B12*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="8">
         <f>IF(A12&lt;=$G$1,MIN(B12,$G$3-C12),"")</f>
         <v/>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="8">
         <f>IF(A12&lt;=$G$1,MAX(0,B12-D12),"")</f>
         <v/>
       </c>
@@ -1622,19 +1755,19 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="8">
         <f>IF(A13&lt;=$G$1,E12,"")</f>
         <v/>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="8">
         <f>IF(A13&lt;=$G$1,B13*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <f>IF(A13&lt;=$G$1,MIN(B13,$G$3-C13),"")</f>
         <v/>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="8">
         <f>IF(A13&lt;=$G$1,MAX(0,B13-D13),"")</f>
         <v/>
       </c>
@@ -1643,19 +1776,19 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="8">
         <f>IF(A14&lt;=$G$1,E13,"")</f>
         <v/>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="8">
         <f>IF(A14&lt;=$G$1,B14*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="8">
         <f>IF(A14&lt;=$G$1,MIN(B14,$G$3-C14),"")</f>
         <v/>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="8">
         <f>IF(A14&lt;=$G$1,MAX(0,B14-D14),"")</f>
         <v/>
       </c>
@@ -1664,19 +1797,19 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="8">
         <f>IF(A15&lt;=$G$1,E14,"")</f>
         <v/>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <f>IF(A15&lt;=$G$1,B15*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <f>IF(A15&lt;=$G$1,MIN(B15,$G$3-C15),"")</f>
         <v/>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <f>IF(A15&lt;=$G$1,MAX(0,B15-D15),"")</f>
         <v/>
       </c>
@@ -1685,19 +1818,19 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="8">
         <f>IF(A16&lt;=$G$1,E15,"")</f>
         <v/>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="8">
         <f>IF(A16&lt;=$G$1,B16*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="8">
         <f>IF(A16&lt;=$G$1,MIN(B16,$G$3-C16),"")</f>
         <v/>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="8">
         <f>IF(A16&lt;=$G$1,MAX(0,B16-D16),"")</f>
         <v/>
       </c>
@@ -1706,19 +1839,19 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="8">
         <f>IF(A17&lt;=$G$1,E16,"")</f>
         <v/>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <f>IF(A17&lt;=$G$1,B17*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <f>IF(A17&lt;=$G$1,MIN(B17,$G$3-C17),"")</f>
         <v/>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <f>IF(A17&lt;=$G$1,MAX(0,B17-D17),"")</f>
         <v/>
       </c>
@@ -1727,19 +1860,19 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="8">
         <f>IF(A18&lt;=$G$1,E17,"")</f>
         <v/>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <f>IF(A18&lt;=$G$1,B18*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <f>IF(A18&lt;=$G$1,MIN(B18,$G$3-C18),"")</f>
         <v/>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <f>IF(A18&lt;=$G$1,MAX(0,B18-D18),"")</f>
         <v/>
       </c>
@@ -1748,19 +1881,19 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="8">
         <f>IF(A19&lt;=$G$1,E18,"")</f>
         <v/>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="8">
         <f>IF(A19&lt;=$G$1,B19*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <f>IF(A19&lt;=$G$1,MIN(B19,$G$3-C19),"")</f>
         <v/>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="8">
         <f>IF(A19&lt;=$G$1,MAX(0,B19-D19),"")</f>
         <v/>
       </c>
@@ -1769,19 +1902,19 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="8">
         <f>IF(A20&lt;=$G$1,E19,"")</f>
         <v/>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <f>IF(A20&lt;=$G$1,B20*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D20" s="7">
+      <c r="D20" s="8">
         <f>IF(A20&lt;=$G$1,MIN(B20,$G$3-C20),"")</f>
         <v/>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="8">
         <f>IF(A20&lt;=$G$1,MAX(0,B20-D20),"")</f>
         <v/>
       </c>
@@ -1790,19 +1923,19 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="8">
         <f>IF(A21&lt;=$G$1,E20,"")</f>
         <v/>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="8">
         <f>IF(A21&lt;=$G$1,B21*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D21" s="7">
+      <c r="D21" s="8">
         <f>IF(A21&lt;=$G$1,MIN(B21,$G$3-C21),"")</f>
         <v/>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="8">
         <f>IF(A21&lt;=$G$1,MAX(0,B21-D21),"")</f>
         <v/>
       </c>
@@ -1811,19 +1944,19 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="8">
         <f>IF(A22&lt;=$G$1,E21,"")</f>
         <v/>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="8">
         <f>IF(A22&lt;=$G$1,B22*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D22" s="7">
+      <c r="D22" s="8">
         <f>IF(A22&lt;=$G$1,MIN(B22,$G$3-C22),"")</f>
         <v/>
       </c>
-      <c r="E22" s="7">
+      <c r="E22" s="8">
         <f>IF(A22&lt;=$G$1,MAX(0,B22-D22),"")</f>
         <v/>
       </c>
@@ -1832,19 +1965,19 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="8">
         <f>IF(A23&lt;=$G$1,E22,"")</f>
         <v/>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="8">
         <f>IF(A23&lt;=$G$1,B23*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="8">
         <f>IF(A23&lt;=$G$1,MIN(B23,$G$3-C23),"")</f>
         <v/>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="8">
         <f>IF(A23&lt;=$G$1,MAX(0,B23-D23),"")</f>
         <v/>
       </c>
@@ -1853,19 +1986,19 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="8">
         <f>IF(A24&lt;=$G$1,E23,"")</f>
         <v/>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="8">
         <f>IF(A24&lt;=$G$1,B24*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="8">
         <f>IF(A24&lt;=$G$1,MIN(B24,$G$3-C24),"")</f>
         <v/>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="8">
         <f>IF(A24&lt;=$G$1,MAX(0,B24-D24),"")</f>
         <v/>
       </c>
@@ -1874,19 +2007,19 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="8">
         <f>IF(A25&lt;=$G$1,E24,"")</f>
         <v/>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="8">
         <f>IF(A25&lt;=$G$1,B25*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D25" s="7">
+      <c r="D25" s="8">
         <f>IF(A25&lt;=$G$1,MIN(B25,$G$3-C25),"")</f>
         <v/>
       </c>
-      <c r="E25" s="7">
+      <c r="E25" s="8">
         <f>IF(A25&lt;=$G$1,MAX(0,B25-D25),"")</f>
         <v/>
       </c>
@@ -1895,19 +2028,19 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="8">
         <f>IF(A26&lt;=$G$1,E25,"")</f>
         <v/>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <f>IF(A26&lt;=$G$1,B26*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="8">
         <f>IF(A26&lt;=$G$1,MIN(B26,$G$3-C26),"")</f>
         <v/>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <f>IF(A26&lt;=$G$1,MAX(0,B26-D26),"")</f>
         <v/>
       </c>
@@ -1916,19 +2049,19 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="8">
         <f>IF(A27&lt;=$G$1,E26,"")</f>
         <v/>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <f>IF(A27&lt;=$G$1,B27*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D27" s="7">
+      <c r="D27" s="8">
         <f>IF(A27&lt;=$G$1,MIN(B27,$G$3-C27),"")</f>
         <v/>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <f>IF(A27&lt;=$G$1,MAX(0,B27-D27),"")</f>
         <v/>
       </c>
@@ -1937,19 +2070,19 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="8">
         <f>IF(A28&lt;=$G$1,E27,"")</f>
         <v/>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <f>IF(A28&lt;=$G$1,B28*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D28" s="7">
+      <c r="D28" s="8">
         <f>IF(A28&lt;=$G$1,MIN(B28,$G$3-C28),"")</f>
         <v/>
       </c>
-      <c r="E28" s="7">
+      <c r="E28" s="8">
         <f>IF(A28&lt;=$G$1,MAX(0,B28-D28),"")</f>
         <v/>
       </c>
@@ -1958,19 +2091,19 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="8">
         <f>IF(A29&lt;=$G$1,E28,"")</f>
         <v/>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="8">
         <f>IF(A29&lt;=$G$1,B29*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="8">
         <f>IF(A29&lt;=$G$1,MIN(B29,$G$3-C29),"")</f>
         <v/>
       </c>
-      <c r="E29" s="7">
+      <c r="E29" s="8">
         <f>IF(A29&lt;=$G$1,MAX(0,B29-D29),"")</f>
         <v/>
       </c>
@@ -1979,19 +2112,19 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="8">
         <f>IF(A30&lt;=$G$1,E29,"")</f>
         <v/>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="8">
         <f>IF(A30&lt;=$G$1,B30*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="8">
         <f>IF(A30&lt;=$G$1,MIN(B30,$G$3-C30),"")</f>
         <v/>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="8">
         <f>IF(A30&lt;=$G$1,MAX(0,B30-D30),"")</f>
         <v/>
       </c>
@@ -2000,19 +2133,19 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="8">
         <f>IF(A31&lt;=$G$1,E30,"")</f>
         <v/>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <f>IF(A31&lt;=$G$1,B31*$G$2,"")</f>
         <v/>
       </c>
-      <c r="D31" s="7">
+      <c r="D31" s="8">
         <f>IF(A31&lt;=$G$1,MIN(B31,$G$3-C31),"")</f>
         <v/>
       </c>
-      <c r="E31" s="7">
+      <c r="E31" s="8">
         <f>IF(A31&lt;=$G$1,MAX(0,B31-D31),"")</f>
         <v/>
       </c>
@@ -2029,7 +2162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2037,120 +2170,144 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="23" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Titre</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Local commercial à vendre près métro Gabriel Péri Asnières</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>Lien</t>
         </is>
       </c>
-      <c r="B2" s="25" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>https://www.geolocaux.com/annonce/local-commercial-a-vendre-pres-metro-gabriel-peri-asnieres-711690.html</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>Ville</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Asnières-sur-Seine (92600)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>geolocaux</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>Première détection</t>
         </is>
       </c>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="29" t="inlineStr">
         <is>
           <t>Murs libres</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>Caractéristiques</t>
         </is>
       </c>
-      <c r="B7" s="24" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Évolution du prix</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>stable depuis la première vue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Fourchette de marché</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>153 ventes réelles 2023-2025 (DVF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
         <is>
           <t>Lecture du prix</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="B10" s="29" t="inlineStr">
         <is>
           <t>Décote sans explication visible dans l'annonce : possible bonne affaire — ou défaut caché (état, copropriété, bail) à vérifier sur place.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>Alertes</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
+      <c r="B11" s="29" t="inlineStr">
         <is>
           <t>loyer_estime</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="110" customHeight="1">
-      <c r="A10" s="23" t="inlineStr">
+    <row r="12" ht="110" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="B10" s="24" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>Ce local de 104 m², en bon état, propose un RDC avec accueil et bureaux ainsi qu'un sous-sol aménageable. Proximité immédiate du métro pour une accessibilité optimale.</t>
         </is>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/07/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +142 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +226 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +226 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +142 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,58 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +142 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +120 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0458</v>
+        <v>0.0475</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 31/08/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,75 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +120 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +101 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.0475</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
+++ b/docs/dossiers/dossier-asnieres-sur-seine-e0140ef8.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
